--- a/today2.xlsx
+++ b/today2.xlsx
@@ -11,317 +11,609 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="201">
   <si>
     <t>email</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="Aptos Narrow"/>
-        <color rgb="FF1155CC"/>
-        <sz val="11.0"/>
-        <u/>
-      </rPr>
-      <t>kanupriya.verma@addverb.com</t>
-    </r>
-  </si>
-  <si>
-    <t>antony.davis@adani.com</t>
-  </si>
-  <si>
-    <t>antra.virmani@thoughtworks.com</t>
-  </si>
-  <si>
-    <t>anu.mhaisalkar@bilcare.com</t>
-  </si>
-  <si>
-    <t>anu@asia.apple.com</t>
-  </si>
-  <si>
-    <t>anu@cgs.cgsmith.soft.net</t>
-  </si>
-  <si>
-    <t>anuj@mindagroup.com</t>
-  </si>
-  <si>
-    <t>anuja.khutwad@ksolves.com</t>
-  </si>
-  <si>
-    <t>anuja.khutwad@ksolves.com </t>
-  </si>
-  <si>
-    <t>anupam.anurag@afcons.com</t>
-  </si>
-  <si>
-    <t>anuradha.kuckian@gep.com</t>
-  </si>
-  <si>
-    <t>anuradha@biopharmax.com</t>
-  </si>
-  <si>
-    <t>anuradhakotlapure1303@gmail.com</t>
-  </si>
-  <si>
-    <t>anuragshukla.hr@gmail.com</t>
-  </si>
-  <si>
-    <t>anurang@giaspn01.vsnl.net.in</t>
-  </si>
-  <si>
-    <t>anusha.bellamkonda@opsramp.com</t>
-  </si>
-  <si>
-    <t>anusha.jain@ralson.com</t>
-  </si>
-  <si>
-    <t>anushka1.sscs@gmail.com</t>
-  </si>
-  <si>
-    <t>anushree.takalkar@ril.com</t>
-  </si>
-  <si>
-    <t>Anusree.Saha@infobip.com</t>
-  </si>
-  <si>
-    <t>ao.pune@centurywells.com</t>
-  </si>
-  <si>
-    <t>aparna.salvi@trizacautomation.com</t>
-  </si>
-  <si>
-    <t>aparna@electropneumatics.com</t>
-  </si>
-  <si>
-    <t>aparna@harchan.com</t>
-  </si>
-  <si>
-    <t>apatel@canaltacontrols.com</t>
-  </si>
-  <si>
-    <t>apcosoft@apcosoft.soft.net</t>
-  </si>
-  <si>
-    <t>APGupta@burnsmcd.in</t>
-  </si>
-  <si>
-    <t>apoorva.chhabra@wipro.com</t>
-  </si>
-  <si>
-    <t>apoorva.kaul@aisglass.com</t>
-  </si>
-  <si>
-    <t>apply@capacite.co.in</t>
-  </si>
-  <si>
-    <t>apply@gmware.com</t>
-  </si>
-  <si>
-    <t>apply@gmware.com </t>
-  </si>
-  <si>
-    <t>appurva.rekhi@publicis.sapient.com</t>
-  </si>
-  <si>
-    <t>aprajita.dubey@salespanda.com</t>
-  </si>
-  <si>
-    <t>aprajita.dubey@salespanda.com </t>
-  </si>
-  <si>
-    <t>apuranik@fulham.com</t>
-  </si>
-  <si>
-    <t>arai@vsnl.com</t>
-  </si>
-  <si>
-    <t>aravind.kumar.krishnasamy@citi.com</t>
-  </si>
-  <si>
-    <t>aravind@hypto.in</t>
-  </si>
-  <si>
-    <t>archana.vissionconsultancy@gmail.com</t>
-  </si>
-  <si>
-    <t>archana.yadav@honeywell.com</t>
-  </si>
-  <si>
-    <t>arg@cypress.com</t>
-  </si>
-  <si>
-    <t>arnold.dmello@quantiphi.com</t>
-  </si>
-  <si>
-    <t>aroskar.deepti@mahindra2wheelers.co</t>
-  </si>
-  <si>
-    <t>ARoy1@intevaproducts.com</t>
-  </si>
-  <si>
-    <t>arpan.shah@rail.bombardier.com</t>
-  </si>
-  <si>
-    <t>arpana.jha@vianaar.com</t>
-  </si>
-  <si>
-    <t>Arpita.Sant@alepo.com</t>
-  </si>
-  <si>
-    <t>arpita.sen@cohesity.com</t>
-  </si>
-  <si>
-    <t>arpita@screen-magic.com</t>
-  </si>
-  <si>
-    <t>arpith.susarla@squareyards.co.in</t>
-  </si>
-  <si>
-    <t>arpurandare@bel.co.in</t>
-  </si>
-  <si>
-    <t>artij@cadence.com</t>
-  </si>
-  <si>
-    <t>arun-za.prasad@ubs.com</t>
-  </si>
-  <si>
-    <t>arun.soman@grupoantolin.com</t>
-  </si>
-  <si>
-    <t>arun@sncpune.com</t>
-  </si>
-  <si>
-    <t>aruna@twinengineers.com</t>
-  </si>
-  <si>
-    <t>arunasree.pobbisetty@continuserve.com</t>
-  </si>
-  <si>
-    <t>arunbhar@cisco.com</t>
-  </si>
-  <si>
-    <t>arunita.sil@danfoss.com</t>
-  </si>
-  <si>
-    <t>arunkapur1@yahoo.co.in</t>
-  </si>
-  <si>
-    <t>arunkumarb@mei.co.in</t>
-  </si>
-  <si>
-    <t>arunp@bajajelectricals.com</t>
-  </si>
-  <si>
-    <t>arunsinghu@hexaware.com</t>
-  </si>
-  <si>
-    <t>arzoo_kureshi@persistent.com</t>
-  </si>
-  <si>
-    <t>arzoo_kureshi@persistent.com </t>
-  </si>
-  <si>
-    <t>as_jadhav@trinityengineers.com</t>
-  </si>
-  <si>
-    <t>ascent@stpb.soft.net</t>
-  </si>
-  <si>
-    <t>asghbd@vsnl.com</t>
-  </si>
-  <si>
-    <t>ashfaq@egbiz.com</t>
-  </si>
-  <si>
-    <t>ashijain0623@gmail.com</t>
-  </si>
-  <si>
-    <t>Ashima.Bhatia@ibm.com</t>
-  </si>
-  <si>
-    <t>ashis@bgl.vsnl.net.in</t>
-  </si>
-  <si>
-    <t>ashis@ccesoft.com</t>
-  </si>
-  <si>
-    <t>ashish.bhanage@veenaindustries.com</t>
-  </si>
-  <si>
-    <t>Ashish.Goyal@larsentoubro.com</t>
-  </si>
-  <si>
-    <t>ashish.jaiswal@ekema.com</t>
-  </si>
-  <si>
-    <t>ashish.nawade@ietl.in</t>
-  </si>
-  <si>
-    <t>ashish.sam@bridgei2i.com</t>
-  </si>
-  <si>
-    <t>Ashish.Shekhar@jswispat.in</t>
-  </si>
-  <si>
-    <t>ashish@mukand.com</t>
-  </si>
-  <si>
-    <t>ashish@mukandsumi.com</t>
-  </si>
-  <si>
-    <t>ashishkapoor@eaton.com</t>
-  </si>
-  <si>
-    <t>ashishshastri@mukand.com</t>
-  </si>
-  <si>
-    <t>ashishsukhadeve@analyticsinsight.net</t>
-  </si>
-  <si>
-    <t>ashok_gandhe@rediffmail.com</t>
-  </si>
-  <si>
-    <t>ashok.b.pabbawar@ril.com</t>
-  </si>
-  <si>
-    <t>ashok.chavan@uni-pol.com</t>
-  </si>
-  <si>
-    <t>ashok.dhotay@kirloskarebara.co.in</t>
-  </si>
-  <si>
-    <t>Ashok.Sadashivan@emerson.com</t>
-  </si>
-  <si>
-    <t>ashok@ratnaafin.com</t>
-  </si>
-  <si>
-    <t>ashrivastava3@vecv.in</t>
-  </si>
-  <si>
-    <t>ashroff@filindia.com</t>
-  </si>
-  <si>
-    <t>ashutosh.chaturvedi@ferrero.com</t>
-  </si>
-  <si>
-    <t>ashutosh.chougule@kalyaniglobal.com</t>
-  </si>
-  <si>
-    <t>ashutosh.nagawade@barclays.com</t>
-  </si>
-  <si>
-    <t>ashutoshc@itwautomotive.in</t>
-  </si>
-  <si>
-    <t>ashwin.ar@ust.com</t>
-  </si>
-  <si>
-    <t>ashwin.vatekar@demagcranes.co.in</t>
-  </si>
-  <si>
-    <t>ashwin@topazpiping.com</t>
+    <t>ashwini.b@encubeethicals.com</t>
+  </si>
+  <si>
+    <t>ashwini.jinke@quest-global.com</t>
+  </si>
+  <si>
+    <t>ashwini.karnawat@abzooba.com</t>
+  </si>
+  <si>
+    <t>ashwini.pareek@hginfra.com</t>
+  </si>
+  <si>
+    <t>ashwinna@amazon.com</t>
+  </si>
+  <si>
+    <t>asiapacific@accord-soft.com</t>
+  </si>
+  <si>
+    <t>asingh@arista.com</t>
+  </si>
+  <si>
+    <t>asinghal@cloudlex.com</t>
+  </si>
+  <si>
+    <t>aslam.parvez@meccalte.in</t>
+  </si>
+  <si>
+    <t>asmi.kulkarni@itcinfotech.com</t>
+  </si>
+  <si>
+    <t>asmita.sambhus@larsentoubro.com</t>
+  </si>
+  <si>
+    <t>Astha@meritshot.com</t>
+  </si>
+  <si>
+    <t>aswin.krishna@gloinnnt.com</t>
+  </si>
+  <si>
+    <t>aswin.krishna@gloinnnt.com </t>
+  </si>
+  <si>
+    <t>atisha.shantinfotech@gmail.com</t>
+  </si>
+  <si>
+    <t>atisha.shantinfotech@gmail.com </t>
+  </si>
+  <si>
+    <t>atkale@simmondsmarshall.com</t>
+  </si>
+  <si>
+    <t>Atul.Chamnikar@forbes.co.in</t>
+  </si>
+  <si>
+    <t>atul.ghumatkar@in.fujikura.com</t>
+  </si>
+  <si>
+    <t>atul.joshi@bekaert.com</t>
+  </si>
+  <si>
+    <t>atul.kabre@ril.com</t>
+  </si>
+  <si>
+    <t>atul.khobragade@birlacentury.com</t>
+  </si>
+  <si>
+    <t>atul.mene@schneider-electric.com</t>
+  </si>
+  <si>
+    <t>atul.pai@in.thomascook.com</t>
+  </si>
+  <si>
+    <t>Atul@menes.in</t>
+  </si>
+  <si>
+    <t>atulamene@yahoo.co.in</t>
+  </si>
+  <si>
+    <t>auditax@satyam.net.in</t>
+  </si>
+  <si>
+    <t>autoel@pn3.vsnl.net.in</t>
+  </si>
+  <si>
+    <t>av_ghugari@trinityengineers.com</t>
+  </si>
+  <si>
+    <t>av.sankar@nism.ac.in</t>
+  </si>
+  <si>
+    <t>avanirshah@gmail.com</t>
+  </si>
+  <si>
+    <t>avanirshah@gmail.com </t>
+  </si>
+  <si>
+    <t>avanthi.m@tekwissen.in</t>
+  </si>
+  <si>
+    <t>avcjindia@vsnl.com</t>
+  </si>
+  <si>
+    <t>avgraine@avesthagen.com</t>
+  </si>
+  <si>
+    <t>avgraine@vsnl.com</t>
+  </si>
+  <si>
+    <t>avinash_bansode@supreme.co.in</t>
+  </si>
+  <si>
+    <t>avinash.arvikar@amtek.com</t>
+  </si>
+  <si>
+    <t>avinash.ganbote@acg-world.com</t>
+  </si>
+  <si>
+    <t>avinash.muley@gmail.com</t>
+  </si>
+  <si>
+    <t>avinash.muley@jci.com</t>
+  </si>
+  <si>
+    <t>avrrao@anz.com</t>
+  </si>
+  <si>
+    <t>avsraghu@cdsblr.co.in</t>
+  </si>
+  <si>
+    <t>ayushrajput8092@gmail.com</t>
+  </si>
+  <si>
+    <t>azisoft@hotmail.com</t>
+  </si>
+  <si>
+    <t>b_sukumar@hp.com</t>
+  </si>
+  <si>
+    <t>B.Nanaware@bagelectronics.com</t>
+  </si>
+  <si>
+    <t>b.prasad@eci.ericsson.se</t>
+  </si>
+  <si>
+    <t>b.sarje@hueco.com</t>
+  </si>
+  <si>
+    <t>Babu_Vitekar@lntenc.com</t>
+  </si>
+  <si>
+    <t>badal.awate@khedcity.com</t>
+  </si>
+  <si>
+    <t>baguld@tii.murugappa.com</t>
+  </si>
+  <si>
+    <t>baisali@recruitcrm.io</t>
+  </si>
+  <si>
+    <t>bajirao.gaji@keihinfie.com</t>
+  </si>
+  <si>
+    <t>bala@foreseemultimedia.com</t>
+  </si>
+  <si>
+    <t>balasaheb.sonawane@bilt.com</t>
+  </si>
+  <si>
+    <t>BALGIM@airproducts.com</t>
+  </si>
+  <si>
+    <t>Baliram.Bodkhe@petrofac.com</t>
+  </si>
+  <si>
+    <t>band.sm@in.bosch.com</t>
+  </si>
+  <si>
+    <t>bangalore.hrd@inf.com</t>
+  </si>
+  <si>
+    <t>bangalore@ho.hclcomnet.co.in</t>
+  </si>
+  <si>
+    <t>bangalore@vxindia.veritas.com</t>
+  </si>
+  <si>
+    <t>barkha.maheshwari@careernet.in</t>
+  </si>
+  <si>
+    <t>basavaraj@premier.co.in</t>
+  </si>
+  <si>
+    <t>basavraj@spmauto.com</t>
+  </si>
+  <si>
+    <t>bazmi.husain@in.abb.com</t>
+  </si>
+  <si>
+    <t>bazmihuzain@in.abb.com</t>
+  </si>
+  <si>
+    <t>bbhagawan@hotmail.com</t>
+  </si>
+  <si>
+    <t>bc@bigtech.org</t>
+  </si>
+  <si>
+    <t>be@net-kraft.com</t>
+  </si>
+  <si>
+    <t>beena.mathew@swarovski.com</t>
+  </si>
+  <si>
+    <t>belop@vsnl.net</t>
+  </si>
+  <si>
+    <t>bewerbung@belectric.com</t>
+  </si>
+  <si>
+    <t>bgk@cimtrix.com</t>
+  </si>
+  <si>
+    <t>bgstech@vsnl.com</t>
+  </si>
+  <si>
+    <t>bhakta@cognosinfotech.com</t>
+  </si>
+  <si>
+    <t>bhangev@gmail.com</t>
+  </si>
+  <si>
+    <t>Bhanu@excelonsolutions.com</t>
+  </si>
+  <si>
+    <t>Bhanu@excelonsolutions.com </t>
+  </si>
+  <si>
+    <t>bhanuc@micron.com</t>
+  </si>
+  <si>
+    <t>bharat_parik@jabil.com</t>
+  </si>
+  <si>
+    <t>bharat.bhamare@force-mtu.com</t>
+  </si>
+  <si>
+    <t>bharat.joshi@practo.com</t>
+  </si>
+  <si>
+    <t>bharat.kumar@tataautocomp.com</t>
+  </si>
+  <si>
+    <t>bharat.sudhesha@yokogawa.com</t>
+  </si>
+  <si>
+    <t>bharat@agarwalpune.com</t>
+  </si>
+  <si>
+    <t>bharat@joveo.com</t>
+  </si>
+  <si>
+    <t>bharath@hgtechinc.net</t>
+  </si>
+  <si>
+    <t>bharath@hgtechinc.net </t>
+  </si>
+  <si>
+    <t>bhargavi.bhatt@ppel.co.in</t>
+  </si>
+  <si>
+    <t>bharti.sharma@feedbackinfra.com</t>
+  </si>
+  <si>
+    <t>Bhaskar.Poman@bremboindia.com</t>
+  </si>
+  <si>
+    <t>bhat.reisha@mahindra.com</t>
+  </si>
+  <si>
+    <t>bhavana.mishra@mindstix.com</t>
+  </si>
+  <si>
+    <t>bhavana@iitjobs.com</t>
+  </si>
+  <si>
+    <t>bhavana@iitjobs.com </t>
+  </si>
+  <si>
+    <t>bhavanadeep@code-brew.com</t>
+  </si>
+  <si>
+    <t>bhavanadeep@code-brew.com </t>
+  </si>
+  <si>
+    <t>Bhavaysh.Karria@giftgujarat.in</t>
+  </si>
+  <si>
+    <t>bhave@boyang-tech.com</t>
+  </si>
+  <si>
+    <t>bhavya.m@nineleaps.com</t>
+  </si>
+  <si>
+    <t>bhetampuria@lntecc.com</t>
+  </si>
+  <si>
+    <t>bhiwareyv@tii.murugappa.com</t>
+  </si>
+  <si>
+    <t>bhoomika.s@sailife.com</t>
+  </si>
+  <si>
+    <t>bhosale.v@brakesindia.co.in</t>
+  </si>
+  <si>
+    <t>bhumika.dahibhate@cleartax.in</t>
+  </si>
+  <si>
+    <t>Bhushan.ambekar@forvia.com</t>
+  </si>
+  <si>
+    <t>bhuvanesh@techwaukee.com</t>
+  </si>
+  <si>
+    <t>bibekananda.badatya@energy-mgt.com</t>
+  </si>
+  <si>
+    <t>biju.sona@alfalaval.com</t>
+  </si>
+  <si>
+    <t>biman.gandhi@autopro.ca</t>
+  </si>
+  <si>
+    <t>Bindu.Surana1@ibm.com</t>
+  </si>
+  <si>
+    <t>binkal.patel@mclindia.com</t>
+  </si>
+  <si>
+    <t>binoy.cherian@continuum.net</t>
+  </si>
+  <si>
+    <t>bipin.c@grinfra.com</t>
+  </si>
+  <si>
+    <t>bk.avasthi@californiadigital.com</t>
+  </si>
+  <si>
+    <t>bkramesh@deindia.com</t>
+  </si>
+  <si>
+    <t>bkuriakose@forbesmarshall.com</t>
+  </si>
+  <si>
+    <t>bmall@mindagroup.com</t>
+  </si>
+  <si>
+    <t>bmtcattle@rediffmail.com</t>
+  </si>
+  <si>
+    <t>bnarasim@baan.com</t>
+  </si>
+  <si>
+    <t>borosil.suman@gmail.com</t>
+  </si>
+  <si>
+    <t>boyang@boyang-tech.com</t>
+  </si>
+  <si>
+    <t>bpatil@westernheatforge.com</t>
+  </si>
+  <si>
+    <t>braval@tibicle.com</t>
+  </si>
+  <si>
+    <t>brigadegroup@vsnl.com</t>
+  </si>
+  <si>
+    <t>brijesh.wahi@celstream.com</t>
+  </si>
+  <si>
+    <t>bshah@incapsulate.com</t>
+  </si>
+  <si>
+    <t>bslisd@giasbg01.vsnl.net.in</t>
+  </si>
+  <si>
+    <t>bstp@melstar.com</t>
+  </si>
+  <si>
+    <t>bunashok@satyam.net.in</t>
+  </si>
+  <si>
+    <t>business@greencitybuildcons.com</t>
+  </si>
+  <si>
+    <t>business@shahpolymers.com</t>
+  </si>
+  <si>
+    <t>c.shivakumar@birlasoft.stpi.soft.net</t>
+  </si>
+  <si>
+    <t>cacenquiry@voltas.com</t>
+  </si>
+  <si>
+    <t>Campus.Recruitment@sunpharma.com</t>
+  </si>
+  <si>
+    <t>campus@aesl.in</t>
+  </si>
+  <si>
+    <t>campusconnect@corecompete.com</t>
+  </si>
+  <si>
+    <t>CampusConnect@tatatechnologies.com</t>
+  </si>
+  <si>
+    <t>campusdrive@crtd.in</t>
+  </si>
+  <si>
+    <t>campusplacements@learningroutes.in</t>
+  </si>
+  <si>
+    <t>campusrecruitment@techouts.com</t>
+  </si>
+  <si>
+    <t>campusrecruitmentmailbox-india@barclays.com</t>
+  </si>
+  <si>
+    <t>captmvdinakar@gmail.com</t>
+  </si>
+  <si>
+    <t>career@anupengg.com</t>
+  </si>
+  <si>
+    <t>career@apcoinfra.com</t>
+  </si>
+  <si>
+    <t>career@bhanwariya.com</t>
+  </si>
+  <si>
+    <t>career@bhartiainfra.com</t>
+  </si>
+  <si>
+    <t>career@codeflies.com</t>
+  </si>
+  <si>
+    <t>career@codeflies.com </t>
+  </si>
+  <si>
+    <t>career@deccanetdesigns.com</t>
+  </si>
+  <si>
+    <t>career@elmex.net</t>
+  </si>
+  <si>
+    <t>career@grinfra.com</t>
+  </si>
+  <si>
+    <t>career@hiso.honeywell</t>
+  </si>
+  <si>
+    <t>career@hiso.honeywell.com</t>
+  </si>
+  <si>
+    <t>career@infosyscareers.com</t>
+  </si>
+  <si>
+    <t>career@infosyscareers.com  </t>
+  </si>
+  <si>
+    <t>career@integramicro.com</t>
+  </si>
+  <si>
+    <t>career@iosandweb.net</t>
+  </si>
+  <si>
+    <t>career@iosandweb.net </t>
+  </si>
+  <si>
+    <t>career@issioln.com</t>
+  </si>
+  <si>
+    <t>career@minimalix.in</t>
+  </si>
+  <si>
+    <t>career@nenpl.in</t>
+  </si>
+  <si>
+    <t>career@nihilent.com</t>
+  </si>
+  <si>
+    <t>career@novell.com</t>
+  </si>
+  <si>
+    <t>career@pcsindia.com</t>
+  </si>
+  <si>
+    <t>career@pspprojects.com</t>
+  </si>
+  <si>
+    <t>career@reputeinfosystems.com</t>
+  </si>
+  <si>
+    <t>career@sapientcodelabs.com</t>
+  </si>
+  <si>
+    <t>career@shulventures.com</t>
+  </si>
+  <si>
+    <t>career@shulventures.com </t>
+  </si>
+  <si>
+    <t>career@sierraopt.com</t>
+  </si>
+  <si>
+    <t>career@sonata-software.com</t>
+  </si>
+  <si>
+    <t>career@starshot.company</t>
+  </si>
+  <si>
+    <t>career@starshot.company </t>
+  </si>
+  <si>
+    <t>career@tatasteel.com</t>
+  </si>
+  <si>
+    <t>career@thetechnkvate.com</t>
+  </si>
+  <si>
+    <t>career@thetechnkvate.com </t>
+  </si>
+  <si>
+    <t>career@tissatech.com</t>
+  </si>
+  <si>
+    <t>career@tristatetechnology.com</t>
+  </si>
+  <si>
+    <t>career@tristatetechnology.com </t>
+  </si>
+  <si>
+    <t>career@zordial.com</t>
+  </si>
+  <si>
+    <t>career1@omnitecheng.com</t>
+  </si>
+  <si>
+    <t>careerb@msdc.hcltech.com</t>
+  </si>
+  <si>
+    <t>careerindia@123india.co</t>
+  </si>
+  <si>
+    <t>careerindia@123india.com</t>
+  </si>
+  <si>
+    <t>careerindia@satyamonline.co</t>
+  </si>
+  <si>
+    <t>careerindia@satyamonline.com</t>
+  </si>
+  <si>
+    <t>careerindia@seraova.com</t>
+  </si>
+  <si>
+    <t>careers_2000@its.soft.net</t>
+  </si>
+  <si>
+    <t>careers.is@inf.com</t>
+  </si>
+  <si>
+    <t>careers.tmcoe@ril.com</t>
+  </si>
+  <si>
+    <t>careers@agumentik.com</t>
+  </si>
+  <si>
+    <t>careers@aizant.com</t>
+  </si>
+  <si>
+    <t>careers@alpex.in</t>
+  </si>
+  <si>
+    <t>careers@apexplustech.com</t>
+  </si>
+  <si>
+    <t>careers@appsteamtechnologies.com</t>
+  </si>
+  <si>
+    <t>careers@appsteamtechnologies.com </t>
+  </si>
+  <si>
+    <t>careers@bhartitelesoft.com</t>
+  </si>
+  <si>
+    <t>careers@blockchainsolutions.network</t>
   </si>
 </sst>
 </file>
@@ -341,10 +633,9 @@
       <name val="Aptos Narrow"/>
     </font>
     <font>
-      <u/>
-      <sz val="11.0"/>
-      <color rgb="FF467886"/>
-      <name val="Aptos Narrow"/>
+      <sz val="9.0"/>
+      <color theme="1"/>
+      <name val="Arial"/>
     </font>
     <font>
       <color theme="1"/>
@@ -361,7 +652,9 @@
       <name val="Calibri"/>
     </font>
     <font>
-      <color theme="1"/>
+      <u/>
+      <sz val="11.0"/>
+      <color rgb="FF467886"/>
       <name val="Aptos Narrow"/>
     </font>
   </fonts>
@@ -391,45 +684,57 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="18">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="1" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="1" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="1" fillId="2" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="1" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="1" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
   </cellXfs>
@@ -664,17 +969,17 @@
       </c>
     </row>
     <row r="3" ht="15.75" customHeight="1">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="4" ht="15.75" customHeight="1">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="5" ht="15.75" customHeight="1">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="4" t="s">
         <v>4</v>
       </c>
     </row>
@@ -684,7 +989,7 @@
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -694,52 +999,52 @@
       </c>
     </row>
     <row r="9" ht="15.75" customHeight="1">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="3" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="10" ht="15.75" customHeight="1">
-      <c r="A10" s="6" t="s">
+      <c r="A10" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="11" ht="15.75" customHeight="1">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="5" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="12" ht="15.75" customHeight="1">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="2" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="13" ht="15.75" customHeight="1">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="6" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="14" ht="15.75" customHeight="1">
-      <c r="A14" s="7" t="s">
+      <c r="A14" s="2" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1">
-      <c r="A15" s="8" t="s">
+      <c r="A15" s="7" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="16" ht="15.75" customHeight="1">
-      <c r="A16" s="5" t="s">
+      <c r="A16" s="2" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="17" ht="15.75" customHeight="1">
-      <c r="A17" s="3" t="s">
+      <c r="A17" s="7" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="18" ht="15.75" customHeight="1">
-      <c r="A18" s="5" t="s">
+      <c r="A18" s="2" t="s">
         <v>17</v>
       </c>
     </row>
@@ -749,22 +1054,22 @@
       </c>
     </row>
     <row r="20" ht="15.75" customHeight="1">
-      <c r="A20" s="3" t="s">
+      <c r="A20" s="2" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="3" t="s">
+      <c r="A21" s="2" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="5" t="s">
+      <c r="A22" s="8" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="3" t="s">
+      <c r="A23" s="2" t="s">
         <v>22</v>
       </c>
     </row>
@@ -779,12 +1084,12 @@
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="3" t="s">
+      <c r="A26" s="5" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="3" t="s">
+      <c r="A27" s="8" t="s">
         <v>26</v>
       </c>
     </row>
@@ -794,7 +1099,7 @@
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" s="3" t="s">
+      <c r="A29" s="2" t="s">
         <v>28</v>
       </c>
     </row>
@@ -804,32 +1109,32 @@
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="4" t="s">
+      <c r="A31" s="3" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="5" t="s">
+      <c r="A32" s="2" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="6" t="s">
+      <c r="A33" s="7" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="34" ht="15.75" customHeight="1">
-      <c r="A34" s="3" t="s">
+      <c r="A34" s="2" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="35" ht="15.75" customHeight="1">
-      <c r="A35" s="5" t="s">
+      <c r="A35" s="2" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="36" ht="15.75" customHeight="1">
-      <c r="A36" s="6" t="s">
+      <c r="A36" s="3" t="s">
         <v>35</v>
       </c>
     </row>
@@ -839,32 +1144,32 @@
       </c>
     </row>
     <row r="38" ht="15.75" customHeight="1">
-      <c r="A38" s="5" t="s">
+      <c r="A38" s="2" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="39" ht="15.75" customHeight="1">
-      <c r="A39" s="5" t="s">
+      <c r="A39" s="2" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="40" ht="15.75" customHeight="1">
-      <c r="A40" s="3" t="s">
+      <c r="A40" s="2" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="41" ht="15.75" customHeight="1">
-      <c r="A41" s="5" t="s">
+      <c r="A41" s="3" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="42" ht="15.75" customHeight="1">
-      <c r="A42" s="3" t="s">
+      <c r="A42" s="8" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="43" ht="15.75" customHeight="1">
-      <c r="A43" s="5" t="s">
+      <c r="A43" s="3" t="s">
         <v>42</v>
       </c>
     </row>
@@ -874,7 +1179,7 @@
       </c>
     </row>
     <row r="45" ht="15.75" customHeight="1">
-      <c r="A45" s="5" t="s">
+      <c r="A45" s="3" t="s">
         <v>44</v>
       </c>
     </row>
@@ -884,12 +1189,12 @@
       </c>
     </row>
     <row r="47" ht="15.75" customHeight="1">
-      <c r="A47" s="3" t="s">
+      <c r="A47" s="2" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="48" ht="15.75" customHeight="1">
-      <c r="A48" s="4" t="s">
+      <c r="A48" s="2" t="s">
         <v>47</v>
       </c>
     </row>
@@ -899,42 +1204,42 @@
       </c>
     </row>
     <row r="50" ht="15.75" customHeight="1">
-      <c r="A50" s="3" t="s">
+      <c r="A50" s="2" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="51" ht="15.75" customHeight="1">
-      <c r="A51" s="3" t="s">
+      <c r="A51" s="8" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="52" ht="15.75" customHeight="1">
-      <c r="A52" s="3" t="s">
+      <c r="A52" s="2" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="53" ht="15.75" customHeight="1">
-      <c r="A53" s="5" t="s">
+      <c r="A53" s="2" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="54" ht="15.75" customHeight="1">
-      <c r="A54" s="4" t="s">
+      <c r="A54" s="5" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="55" ht="15.75" customHeight="1">
-      <c r="A55" s="3" t="s">
+      <c r="A55" s="2" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="56" ht="15.75" customHeight="1">
-      <c r="A56" s="5" t="s">
+      <c r="A56" s="2" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="57" ht="15.75" customHeight="1">
-      <c r="A57" s="5" t="s">
+      <c r="A57" s="3" t="s">
         <v>56</v>
       </c>
     </row>
@@ -944,7 +1249,7 @@
       </c>
     </row>
     <row r="59" ht="15.75" customHeight="1">
-      <c r="A59" s="5" t="s">
+      <c r="A59" s="3" t="s">
         <v>58</v>
       </c>
     </row>
@@ -954,52 +1259,52 @@
       </c>
     </row>
     <row r="61" ht="15.75" customHeight="1">
-      <c r="A61" s="3" t="s">
+      <c r="A61" s="2" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="62" ht="15.75" customHeight="1">
-      <c r="A62" s="5" t="s">
+      <c r="A62" s="2" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="63" ht="15.75" customHeight="1">
-      <c r="A63" s="3" t="s">
+      <c r="A63" s="9" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="64" ht="15.75" customHeight="1">
-      <c r="A64" s="5" t="s">
+      <c r="A64" s="10" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="65" ht="15.75" customHeight="1">
-      <c r="A65" s="5" t="s">
+      <c r="A65" s="10" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="66" ht="15.75" customHeight="1">
-      <c r="A66" s="5" t="s">
+      <c r="A66" s="10" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="67" ht="15.75" customHeight="1">
-      <c r="A67" s="6" t="s">
+      <c r="A67" s="11" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="68" ht="15.75" customHeight="1">
-      <c r="A68" s="5" t="s">
+      <c r="A68" s="9" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="69" ht="15.75" customHeight="1">
-      <c r="A69" s="9" t="s">
+      <c r="A69" s="10" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="70" ht="15.75" customHeight="1">
-      <c r="A70" s="9" t="s">
+      <c r="A70" s="11" t="s">
         <v>69</v>
       </c>
     </row>
@@ -1014,57 +1319,57 @@
       </c>
     </row>
     <row r="73" ht="15.75" customHeight="1">
-      <c r="A73" s="11" t="s">
+      <c r="A73" s="10" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="74" ht="15.75" customHeight="1">
-      <c r="A74" s="9" t="s">
+      <c r="A74" s="11" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="75" ht="15.75" customHeight="1">
-      <c r="A75" s="9" t="s">
+      <c r="A75" s="10" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="76" ht="15.75" customHeight="1">
-      <c r="A76" s="11" t="s">
+      <c r="A76" s="10" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="77" ht="15.75" customHeight="1">
-      <c r="A77" s="9" t="s">
+      <c r="A77" s="10" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="78" ht="15.75" customHeight="1">
-      <c r="A78" s="11" t="s">
+      <c r="A78" s="10" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="79" ht="15.75" customHeight="1">
-      <c r="A79" s="12" t="s">
+      <c r="A79" s="10" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="80" ht="15.75" customHeight="1">
-      <c r="A80" s="9" t="s">
+      <c r="A80" s="12" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="81" ht="15.75" customHeight="1">
-      <c r="A81" s="9" t="s">
+      <c r="A81" s="13" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="82" ht="15.75" customHeight="1">
-      <c r="A82" s="9" t="s">
+      <c r="A82" s="10" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="83" ht="15.75" customHeight="1">
-      <c r="A83" s="9" t="s">
+      <c r="A83" s="10" t="s">
         <v>82</v>
       </c>
     </row>
@@ -1074,47 +1379,47 @@
       </c>
     </row>
     <row r="85" ht="15.75" customHeight="1">
-      <c r="A85" s="9" t="s">
+      <c r="A85" s="14" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="86" ht="15.75" customHeight="1">
-      <c r="A86" s="9" t="s">
+      <c r="A86" s="11" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="87" ht="15.75" customHeight="1">
-      <c r="A87" s="11" t="s">
+      <c r="A87" s="10" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="88" ht="15.75" customHeight="1">
-      <c r="A88" s="9" t="s">
+      <c r="A88" s="11" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="89" ht="15.75" customHeight="1">
-      <c r="A89" s="11" t="s">
+      <c r="A89" s="10" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="90" ht="15.75" customHeight="1">
-      <c r="A90" s="11" t="s">
+      <c r="A90" s="12" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="91" ht="15.75" customHeight="1">
-      <c r="A91" s="9" t="s">
+      <c r="A91" s="14" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="92" ht="15.75" customHeight="1">
-      <c r="A92" s="9" t="s">
+      <c r="A92" s="10" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="93" ht="15.75" customHeight="1">
-      <c r="A93" s="9" t="s">
+      <c r="A93" s="10" t="s">
         <v>92</v>
       </c>
     </row>
@@ -1124,27 +1429,27 @@
       </c>
     </row>
     <row r="95" ht="15.75" customHeight="1">
-      <c r="A95" s="11" t="s">
+      <c r="A95" s="14" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="96" ht="15.75" customHeight="1">
-      <c r="A96" s="11" t="s">
+      <c r="A96" s="10" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="97" ht="15.75" customHeight="1">
-      <c r="A97" s="11" t="s">
+      <c r="A97" s="12" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="98" ht="15.75" customHeight="1">
-      <c r="A98" s="11" t="s">
+      <c r="A98" s="10" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="99" ht="15.75" customHeight="1">
-      <c r="A99" s="11" t="s">
+      <c r="A99" s="12" t="s">
         <v>98</v>
       </c>
     </row>
@@ -1154,110 +1459,510 @@
       </c>
     </row>
     <row r="101" ht="15.75" customHeight="1">
-      <c r="A101" s="13" t="s">
+      <c r="A101" s="11" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="102" ht="15.75" customHeight="1"/>
-    <row r="103" ht="15.75" customHeight="1"/>
-    <row r="104" ht="15.75" customHeight="1"/>
-    <row r="105" ht="15.75" customHeight="1"/>
-    <row r="106" ht="15.75" customHeight="1"/>
-    <row r="107" ht="15.75" customHeight="1"/>
-    <row r="108" ht="15.75" customHeight="1"/>
-    <row r="109" ht="15.75" customHeight="1"/>
-    <row r="110" ht="15.75" customHeight="1"/>
-    <row r="111" ht="15.75" customHeight="1"/>
-    <row r="112" ht="15.75" customHeight="1"/>
-    <row r="113" ht="15.75" customHeight="1"/>
-    <row r="114" ht="15.75" customHeight="1"/>
-    <row r="115" ht="15.75" customHeight="1"/>
-    <row r="116" ht="15.75" customHeight="1"/>
-    <row r="117" ht="15.75" customHeight="1"/>
-    <row r="118" ht="15.75" customHeight="1"/>
-    <row r="119" ht="15.75" customHeight="1"/>
-    <row r="120" ht="15.75" customHeight="1"/>
-    <row r="121" ht="15.75" customHeight="1"/>
-    <row r="122" ht="15.75" customHeight="1"/>
-    <row r="123" ht="15.75" customHeight="1"/>
-    <row r="124" ht="15.75" customHeight="1"/>
-    <row r="125" ht="15.75" customHeight="1"/>
-    <row r="126" ht="15.75" customHeight="1"/>
-    <row r="127" ht="15.75" customHeight="1"/>
-    <row r="128" ht="15.75" customHeight="1"/>
-    <row r="129" ht="15.75" customHeight="1"/>
-    <row r="130" ht="15.75" customHeight="1"/>
-    <row r="131" ht="15.75" customHeight="1"/>
-    <row r="132" ht="15.75" customHeight="1"/>
-    <row r="133" ht="15.75" customHeight="1"/>
-    <row r="134" ht="15.75" customHeight="1"/>
-    <row r="135" ht="15.75" customHeight="1"/>
-    <row r="136" ht="15.75" customHeight="1"/>
-    <row r="137" ht="15.75" customHeight="1"/>
-    <row r="138" ht="15.75" customHeight="1"/>
-    <row r="139" ht="15.75" customHeight="1"/>
-    <row r="140" ht="15.75" customHeight="1"/>
-    <row r="141" ht="15.75" customHeight="1"/>
-    <row r="142" ht="15.75" customHeight="1"/>
-    <row r="143" ht="15.75" customHeight="1"/>
-    <row r="144" ht="15.75" customHeight="1"/>
-    <row r="145" ht="15.75" customHeight="1"/>
-    <row r="146" ht="15.75" customHeight="1"/>
-    <row r="147" ht="15.75" customHeight="1"/>
-    <row r="148" ht="15.75" customHeight="1"/>
-    <row r="149" ht="15.75" customHeight="1"/>
-    <row r="150" ht="15.75" customHeight="1"/>
-    <row r="151" ht="15.75" customHeight="1"/>
-    <row r="152" ht="15.75" customHeight="1"/>
-    <row r="153" ht="15.75" customHeight="1"/>
-    <row r="154" ht="15.75" customHeight="1"/>
-    <row r="155" ht="15.75" customHeight="1"/>
-    <row r="156" ht="15.75" customHeight="1"/>
-    <row r="157" ht="15.75" customHeight="1"/>
-    <row r="158" ht="15.75" customHeight="1"/>
-    <row r="159" ht="15.75" customHeight="1"/>
-    <row r="160" ht="15.75" customHeight="1"/>
-    <row r="161" ht="15.75" customHeight="1"/>
-    <row r="162" ht="15.75" customHeight="1"/>
-    <row r="163" ht="15.75" customHeight="1"/>
-    <row r="164" ht="15.75" customHeight="1"/>
-    <row r="165" ht="15.75" customHeight="1"/>
-    <row r="166" ht="15.75" customHeight="1"/>
-    <row r="167" ht="15.75" customHeight="1"/>
-    <row r="168" ht="15.75" customHeight="1"/>
-    <row r="169" ht="15.75" customHeight="1"/>
-    <row r="170" ht="15.75" customHeight="1"/>
-    <row r="171" ht="15.75" customHeight="1"/>
-    <row r="172" ht="15.75" customHeight="1"/>
-    <row r="173" ht="15.75" customHeight="1"/>
-    <row r="174" ht="15.75" customHeight="1"/>
-    <row r="175" ht="15.75" customHeight="1"/>
-    <row r="176" ht="15.75" customHeight="1"/>
-    <row r="177" ht="15.75" customHeight="1"/>
-    <row r="178" ht="15.75" customHeight="1"/>
-    <row r="179" ht="15.75" customHeight="1"/>
-    <row r="180" ht="15.75" customHeight="1"/>
-    <row r="181" ht="15.75" customHeight="1"/>
-    <row r="182" ht="15.75" customHeight="1"/>
-    <row r="183" ht="15.75" customHeight="1"/>
-    <row r="184" ht="15.75" customHeight="1"/>
-    <row r="185" ht="15.75" customHeight="1"/>
-    <row r="186" ht="15.75" customHeight="1"/>
-    <row r="187" ht="15.75" customHeight="1"/>
-    <row r="188" ht="15.75" customHeight="1"/>
-    <row r="189" ht="15.75" customHeight="1"/>
-    <row r="190" ht="15.75" customHeight="1"/>
-    <row r="191" ht="15.75" customHeight="1"/>
-    <row r="192" ht="15.75" customHeight="1"/>
-    <row r="193" ht="15.75" customHeight="1"/>
-    <row r="194" ht="15.75" customHeight="1"/>
-    <row r="195" ht="15.75" customHeight="1"/>
-    <row r="196" ht="15.75" customHeight="1"/>
-    <row r="197" ht="15.75" customHeight="1"/>
-    <row r="198" ht="15.75" customHeight="1"/>
-    <row r="199" ht="15.75" customHeight="1"/>
-    <row r="200" ht="15.75" customHeight="1"/>
-    <row r="201" ht="15.75" customHeight="1"/>
+    <row r="102" ht="15.75" customHeight="1">
+      <c r="A102" s="9" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="103" ht="15.75" customHeight="1">
+      <c r="A103" s="11" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="104" ht="15.75" customHeight="1">
+      <c r="A104" s="10" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="105" ht="15.75" customHeight="1">
+      <c r="A105" s="11" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="106" ht="15.75" customHeight="1">
+      <c r="A106" s="10" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="107" ht="15.75" customHeight="1">
+      <c r="A107" s="11" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="108" ht="15.75" customHeight="1">
+      <c r="A108" s="14" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="109" ht="15.75" customHeight="1">
+      <c r="A109" s="11" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="110" ht="15.75" customHeight="1">
+      <c r="A110" s="13" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="111" ht="15.75" customHeight="1">
+      <c r="A111" s="11" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="112" ht="15.75" customHeight="1">
+      <c r="A112" s="11" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="113" ht="15.75" customHeight="1">
+      <c r="A113" s="15" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="114" ht="15.75" customHeight="1">
+      <c r="A114" s="10" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="115" ht="15.75" customHeight="1">
+      <c r="A115" s="11" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="116" ht="15.75" customHeight="1">
+      <c r="A116" s="10" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="117" ht="15.75" customHeight="1">
+      <c r="A117" s="11" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="118" ht="15.75" customHeight="1">
+      <c r="A118" s="10" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="119" ht="15.75" customHeight="1">
+      <c r="A119" s="10" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="120" ht="15.75" customHeight="1">
+      <c r="A120" s="11" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="121" ht="15.75" customHeight="1">
+      <c r="A121" s="10" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="122" ht="15.75" customHeight="1">
+      <c r="A122" s="11" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="123" ht="15.75" customHeight="1">
+      <c r="A123" s="14" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="124" ht="15.75" customHeight="1">
+      <c r="A124" s="11" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="125" ht="15.75" customHeight="1">
+      <c r="A125" s="10" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="126" ht="15.75" customHeight="1">
+      <c r="A126" s="11" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="127" ht="15.75" customHeight="1">
+      <c r="A127" s="11" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="128" ht="15.75" customHeight="1">
+      <c r="A128" s="11" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="129" ht="15.75" customHeight="1">
+      <c r="A129" s="11" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="130" ht="15.75" customHeight="1">
+      <c r="A130" s="11" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="131" ht="15.75" customHeight="1">
+      <c r="A131" s="10" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="132" ht="15.75" customHeight="1">
+      <c r="A132" s="10" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="133" ht="15.75" customHeight="1">
+      <c r="A133" s="11" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="134" ht="15.75" customHeight="1">
+      <c r="A134" s="10" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="135" ht="15.75" customHeight="1">
+      <c r="A135" s="11" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="136" ht="15.75" customHeight="1">
+      <c r="A136" s="10" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="137" ht="15.75" customHeight="1">
+      <c r="A137" s="11" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="138" ht="15.75" customHeight="1">
+      <c r="A138" s="11" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="139" ht="15.75" customHeight="1">
+      <c r="A139" s="11" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="140" ht="15.75" customHeight="1">
+      <c r="A140" s="11" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="141" ht="15.75" customHeight="1">
+      <c r="A141" s="11" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="142" ht="15.75" customHeight="1">
+      <c r="A142" s="14" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="143" ht="15.75" customHeight="1">
+      <c r="A143" s="14" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="144" ht="15.75" customHeight="1">
+      <c r="A144" s="11" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="145" ht="15.75" customHeight="1">
+      <c r="A145" s="11" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="146" ht="15.75" customHeight="1">
+      <c r="A146" s="14" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="147" ht="15.75" customHeight="1">
+      <c r="A147" s="16" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="148" ht="15.75" customHeight="1">
+      <c r="A148" s="10" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="149" ht="15.75" customHeight="1">
+      <c r="A149" s="10" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="150" ht="15.75" customHeight="1">
+      <c r="A150" s="10" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="151" ht="15.75" customHeight="1">
+      <c r="A151" s="12" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="152" ht="15.75" customHeight="1">
+      <c r="A152" s="10" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="153" ht="15.75" customHeight="1">
+      <c r="A153" s="14" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="154" ht="15.75" customHeight="1">
+      <c r="A154" s="10" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="155" ht="15.75" customHeight="1">
+      <c r="A155" s="9" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="156" ht="15.75" customHeight="1">
+      <c r="A156" s="9" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="157" ht="15.75" customHeight="1">
+      <c r="A157" s="9" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="158" ht="15.75" customHeight="1">
+      <c r="A158" s="12" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="159" ht="15.75" customHeight="1">
+      <c r="A159" s="10" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="160" ht="15.75" customHeight="1">
+      <c r="A160" s="9" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="161" ht="15.75" customHeight="1">
+      <c r="A161" s="12" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="162" ht="15.75" customHeight="1">
+      <c r="A162" s="11" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="163" ht="15.75" customHeight="1">
+      <c r="A163" s="17" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="164" ht="15.75" customHeight="1">
+      <c r="A164" s="10" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="165" ht="15.75" customHeight="1">
+      <c r="A165" s="10" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="166" ht="15.75" customHeight="1">
+      <c r="A166" s="9" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="167" ht="15.75" customHeight="1">
+      <c r="A167" s="16" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="168" ht="15.75" customHeight="1">
+      <c r="A168" s="10" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="169" ht="15.75" customHeight="1">
+      <c r="A169" s="10" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="170" ht="15.75" customHeight="1">
+      <c r="A170" s="10" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="171" ht="15.75" customHeight="1">
+      <c r="A171" s="10" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="172" ht="15.75" customHeight="1">
+      <c r="A172" s="12" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="173" ht="15.75" customHeight="1">
+      <c r="A173" s="10" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="174" ht="15.75" customHeight="1">
+      <c r="A174" s="10" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="175" ht="15.75" customHeight="1">
+      <c r="A175" s="10" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="176" ht="15.75" customHeight="1">
+      <c r="A176" s="12" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="177" ht="15.75" customHeight="1">
+      <c r="A177" s="14" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="178" ht="15.75" customHeight="1">
+      <c r="A178" s="10" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="179" ht="15.75" customHeight="1">
+      <c r="A179" s="12" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="180" ht="15.75" customHeight="1">
+      <c r="A180" s="10" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="181" ht="15.75" customHeight="1">
+      <c r="A181" s="10" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="182" ht="15.75" customHeight="1">
+      <c r="A182" s="12" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="183" ht="15.75" customHeight="1">
+      <c r="A183" s="10" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="184" ht="15.75" customHeight="1">
+      <c r="A184" s="10" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="185" ht="15.75" customHeight="1">
+      <c r="A185" s="9" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="186" ht="15.75" customHeight="1">
+      <c r="A186" s="9" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="187" ht="15.75" customHeight="1">
+      <c r="A187" s="9" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="188" ht="15.75" customHeight="1">
+      <c r="A188" s="9" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="189" ht="15.75" customHeight="1">
+      <c r="A189" s="9" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="190" ht="15.75" customHeight="1">
+      <c r="A190" s="10" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="191" ht="15.75" customHeight="1">
+      <c r="A191" s="10" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="192" ht="15.75" customHeight="1">
+      <c r="A192" s="9" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="193" ht="15.75" customHeight="1">
+      <c r="A193" s="10" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="194" ht="15.75" customHeight="1">
+      <c r="A194" s="11" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="195" ht="15.75" customHeight="1">
+      <c r="A195" s="9" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="196" ht="15.75" customHeight="1">
+      <c r="A196" s="10" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="197" ht="15.75" customHeight="1">
+      <c r="A197" s="10" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="198" ht="15.75" customHeight="1">
+      <c r="A198" s="10" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="199" ht="15.75" customHeight="1">
+      <c r="A199" s="12" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="200" ht="15.75" customHeight="1">
+      <c r="A200" s="10" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="201" ht="15.75" customHeight="1">
+      <c r="A201" s="9" t="s">
+        <v>200</v>
+      </c>
+    </row>
     <row r="202" ht="15.75" customHeight="1"/>
     <row r="203" ht="15.75" customHeight="1"/>
     <row r="204" ht="15.75" customHeight="1"/>
@@ -1398,109 +2103,9 @@
     <row r="339" ht="15.75" customHeight="1"/>
     <row r="340" ht="15.75" customHeight="1"/>
     <row r="341" ht="15.75" customHeight="1"/>
-    <row r="342" ht="15.75" customHeight="1"/>
-    <row r="343" ht="15.75" customHeight="1"/>
-    <row r="344" ht="15.75" customHeight="1"/>
-    <row r="345" ht="15.75" customHeight="1"/>
-    <row r="346" ht="15.75" customHeight="1"/>
-    <row r="347" ht="15.75" customHeight="1"/>
-    <row r="348" ht="15.75" customHeight="1"/>
-    <row r="349" ht="15.75" customHeight="1"/>
-    <row r="350" ht="15.75" customHeight="1"/>
-    <row r="351" ht="15.75" customHeight="1"/>
-    <row r="352" ht="15.75" customHeight="1"/>
-    <row r="353" ht="15.75" customHeight="1"/>
-    <row r="354" ht="15.75" customHeight="1"/>
-    <row r="355" ht="15.75" customHeight="1"/>
-    <row r="356" ht="15.75" customHeight="1"/>
-    <row r="357" ht="15.75" customHeight="1"/>
-    <row r="358" ht="15.75" customHeight="1"/>
-    <row r="359" ht="15.75" customHeight="1"/>
-    <row r="360" ht="15.75" customHeight="1"/>
-    <row r="361" ht="15.75" customHeight="1"/>
-    <row r="362" ht="15.75" customHeight="1"/>
-    <row r="363" ht="15.75" customHeight="1"/>
-    <row r="364" ht="15.75" customHeight="1"/>
-    <row r="365" ht="15.75" customHeight="1"/>
-    <row r="366" ht="15.75" customHeight="1"/>
-    <row r="367" ht="15.75" customHeight="1"/>
-    <row r="368" ht="15.75" customHeight="1"/>
-    <row r="369" ht="15.75" customHeight="1"/>
-    <row r="370" ht="15.75" customHeight="1"/>
-    <row r="371" ht="15.75" customHeight="1"/>
-    <row r="372" ht="15.75" customHeight="1"/>
-    <row r="373" ht="15.75" customHeight="1"/>
-    <row r="374" ht="15.75" customHeight="1"/>
-    <row r="375" ht="15.75" customHeight="1"/>
-    <row r="376" ht="15.75" customHeight="1"/>
-    <row r="377" ht="15.75" customHeight="1"/>
-    <row r="378" ht="15.75" customHeight="1"/>
-    <row r="379" ht="15.75" customHeight="1"/>
-    <row r="380" ht="15.75" customHeight="1"/>
-    <row r="381" ht="15.75" customHeight="1"/>
-    <row r="382" ht="15.75" customHeight="1"/>
-    <row r="383" ht="15.75" customHeight="1"/>
-    <row r="384" ht="15.75" customHeight="1"/>
-    <row r="385" ht="15.75" customHeight="1"/>
-    <row r="386" ht="15.75" customHeight="1"/>
-    <row r="387" ht="15.75" customHeight="1"/>
-    <row r="388" ht="15.75" customHeight="1"/>
-    <row r="389" ht="15.75" customHeight="1"/>
-    <row r="390" ht="15.75" customHeight="1"/>
-    <row r="391" ht="15.75" customHeight="1"/>
-    <row r="392" ht="15.75" customHeight="1"/>
-    <row r="393" ht="15.75" customHeight="1"/>
-    <row r="394" ht="15.75" customHeight="1"/>
-    <row r="395" ht="15.75" customHeight="1"/>
-    <row r="396" ht="15.75" customHeight="1"/>
-    <row r="397" ht="15.75" customHeight="1"/>
-    <row r="398" ht="15.75" customHeight="1"/>
-    <row r="399" ht="15.75" customHeight="1"/>
-    <row r="400" ht="15.75" customHeight="1"/>
-    <row r="401" ht="15.75" customHeight="1"/>
-    <row r="402" ht="15.75" customHeight="1"/>
-    <row r="403" ht="15.75" customHeight="1"/>
-    <row r="404" ht="15.75" customHeight="1"/>
-    <row r="405" ht="15.75" customHeight="1"/>
-    <row r="406" ht="15.75" customHeight="1"/>
-    <row r="407" ht="15.75" customHeight="1"/>
-    <row r="408" ht="15.75" customHeight="1"/>
-    <row r="409" ht="15.75" customHeight="1"/>
-    <row r="410" ht="15.75" customHeight="1"/>
-    <row r="411" ht="15.75" customHeight="1"/>
-    <row r="412" ht="15.75" customHeight="1"/>
-    <row r="413" ht="15.75" customHeight="1"/>
-    <row r="414" ht="15.75" customHeight="1"/>
-    <row r="415" ht="15.75" customHeight="1"/>
-    <row r="416" ht="15.75" customHeight="1"/>
-    <row r="417" ht="15.75" customHeight="1"/>
-    <row r="418" ht="15.75" customHeight="1"/>
-    <row r="419" ht="15.75" customHeight="1"/>
-    <row r="420" ht="15.75" customHeight="1"/>
-    <row r="421" ht="15.75" customHeight="1"/>
-    <row r="422" ht="15.75" customHeight="1"/>
-    <row r="423" ht="15.75" customHeight="1"/>
-    <row r="424" ht="15.75" customHeight="1"/>
-    <row r="425" ht="15.75" customHeight="1"/>
-    <row r="426" ht="15.75" customHeight="1"/>
-    <row r="427" ht="15.75" customHeight="1"/>
-    <row r="428" ht="15.75" customHeight="1"/>
-    <row r="429" ht="15.75" customHeight="1"/>
-    <row r="430" ht="15.75" customHeight="1"/>
-    <row r="431" ht="15.75" customHeight="1"/>
-    <row r="432" ht="15.75" customHeight="1"/>
-    <row r="433" ht="15.75" customHeight="1"/>
-    <row r="434" ht="15.75" customHeight="1"/>
-    <row r="435" ht="15.75" customHeight="1"/>
-    <row r="436" ht="15.75" customHeight="1"/>
-    <row r="437" ht="15.75" customHeight="1"/>
-    <row r="438" ht="15.75" customHeight="1"/>
-    <row r="439" ht="15.75" customHeight="1"/>
-    <row r="440" ht="15.75" customHeight="1"/>
-    <row r="441" ht="15.75" customHeight="1"/>
   </sheetData>
   <hyperlinks>
-    <hyperlink r:id="rId1" ref="A2"/>
+    <hyperlink r:id="rId1" ref="A163"/>
   </hyperlinks>
   <printOptions/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
